--- a/data/trans_camb/P36BPD07_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P36BPD07_R-Clase-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>-10,73</t>
+          <t>-11,49</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-4,32</t>
+          <t>-5,27</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,75</t>
+          <t>-8,6</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,54; -6,41</t>
+          <t>-15,7; -6,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -0,09</t>
+          <t>-9,65; -0,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,94; -4,47</t>
+          <t>-11,86; -5,29</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>-11,85%</t>
+          <t>-12,69%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-4,84%</t>
+          <t>-5,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-8,62%</t>
+          <t>-9,56%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -7,46</t>
+          <t>-17,04; -7,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,72; -0,09</t>
+          <t>-10,61; -0,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,96; -5,09</t>
+          <t>-12,99; -6,03</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>-13,03</t>
+          <t>-13,5</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-6,94</t>
+          <t>-7,47</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-10,18</t>
+          <t>-10,64</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,45; -7,7</t>
+          <t>-18,58; -7,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; -1,96</t>
+          <t>-12,28; -2,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -6,52</t>
+          <t>-14,73; -7,07</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>-14,83%</t>
+          <t>-15,37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-8,05%</t>
+          <t>-8,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-11,69%</t>
+          <t>-12,22%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,39; -8,97</t>
+          <t>-20,74; -9,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,76; -2,41</t>
+          <t>-13,91; -2,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,92; -7,56</t>
+          <t>-16,84; -8,33</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>-4,46</t>
+          <t>-15,49</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-8,66</t>
+          <t>-9,07</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-13,63</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 8,18</t>
+          <t>-20,55; -10,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,16; -0,55</t>
+          <t>-16,0; -1,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 7,39</t>
+          <t>-17,84; -8,92</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>-5,19%</t>
+          <t>-18,05%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-10,02%</t>
+          <t>-10,48%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-6,19%</t>
+          <t>-15,85%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 9,83</t>
+          <t>-23,56; -11,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -0,65</t>
+          <t>-17,93; -2,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 8,78</t>
+          <t>-20,49; -10,66</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>-14,78</t>
+          <t>-14,34</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-2,3</t>
+          <t>-7,91</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-8,81</t>
+          <t>-11,58</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-18,27; -10,39</t>
+          <t>-18,07; -10,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,74; 8,34</t>
+          <t>-11,57; -4,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -1,47</t>
+          <t>-14,32; -9,0</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>-17,39%</t>
+          <t>-16,88%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-2,75%</t>
+          <t>-9,46%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-10,44%</t>
+          <t>-13,73%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -12,31</t>
+          <t>-20,84; -12,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 10,28</t>
+          <t>-13,78; -5,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-15,14; -1,74</t>
+          <t>-16,8; -10,84</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>-18,58</t>
+          <t>-18,32</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-8,56</t>
+          <t>-11,97</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-11,9</t>
+          <t>-14,4</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,83; -12,88</t>
+          <t>-23,73; -13,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-12,76; -2,9</t>
+          <t>-15,59; -8,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-15,43; -6,54</t>
+          <t>-17,35; -11,38</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>-22,1%</t>
+          <t>-21,78%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-9,85%</t>
+          <t>-13,76%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-13,89%</t>
+          <t>-16,81%</t>
         </is>
       </c>
     </row>
@@ -1001,24 +1001,24 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-29,32; -15,64</t>
+          <t>-27,66; -15,76</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -3,32</t>
+          <t>-17,61; -9,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-17,84; -7,89</t>
+          <t>-19,96; -13,39</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1028,17 +1028,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4,66</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>-15,1</t>
+          <t>-16,03</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-11,0</t>
+          <t>-12,61</t>
         </is>
       </c>
     </row>
@@ -1051,17 +1051,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 15,88</t>
+          <t>-10,88; 10,46</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-18,79; -11,2</t>
+          <t>-19,66; -12,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-14,8; -7,41</t>
+          <t>-16,46; -8,95</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>-17,11%</t>
+          <t>-18,16%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-13,14%</t>
+          <t>-15,08%</t>
         </is>
       </c>
     </row>
@@ -1097,17 +1097,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 25,63</t>
+          <t>-16,1; 16,46</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-21,09; -12,8</t>
+          <t>-22,02; -14,09</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-17,4; -8,85</t>
+          <t>-19,49; -10,85</t>
         </is>
       </c>
     </row>
@@ -1124,17 +1124,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>-10,52</t>
+          <t>-13,0</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>-7,74</t>
+          <t>-10,41</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-9,08</t>
+          <t>-11,66</t>
         </is>
       </c>
     </row>
@@ -1147,17 +1147,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-13,48; -4,03</t>
+          <t>-15,07; -10,78</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,96; -3,68</t>
+          <t>-12,31; -8,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-11,04; -5,54</t>
+          <t>-12,96; -10,39</t>
         </is>
       </c>
     </row>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>-12,47%</t>
+          <t>-15,4%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>-8,93%</t>
+          <t>-12,01%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-10,61%</t>
+          <t>-13,63%</t>
         </is>
       </c>
     </row>
@@ -1193,17 +1193,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-15,89; -4,54</t>
+          <t>-17,7; -12,92</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-11,41; -4,27</t>
+          <t>-14,07; -10,16</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-12,9; -6,58</t>
+          <t>-15,03; -12,21</t>
         </is>
       </c>
     </row>
